--- a/vse-loti/340996426/spec-340996426.xlsx
+++ b/vse-loti/340996426/spec-340996426.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spec" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НМЦК" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.####"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +30,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +66,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,21 +467,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15.28515625" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20.28515625" customWidth="1" min="7" max="7"/>
+    <col width="18.85546875" customWidth="1" min="8" max="8"/>
+    <col width="16.42578125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -482,226 +529,250 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Труба 102×12, ст 20 ГОСТ 8732-78 / 8731-74</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Труба 102х12, ст 20 ГОСТ 8732-78 / 8731-74</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>102×12</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>330</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.33</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Труба 16×1,2, ст 20 ГОСТ 10704-91 / 10705-80</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Труба 16х1,2, ст 20 ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>16×1.2</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.003</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Труба 180×10, 345-12-09Г2С-ГС ГОСТ 8732-78 / 19281-2014</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Труба 180х10, 345-12-09Г2С-ГС ГОСТ 8732-78 / 19281-2014</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>180×10</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="4" t="n">
         <v>0.252</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Труба 18×2, ст. 20 ГОСТ 8734-75 / 8733-74</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Труба 18х2, ст. 20 ГОСТ 8734-75 / 8733-74</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>18×2</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="4" t="n">
         <v>0.008999999999999999</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Труба 34×3, ст. 20 ГОСТ 8734-75 / 8733-74</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Труба 34х3, ст. 20 ГОСТ 8734-75 / 8733-74</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>34×3</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.025</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Труба 60×8, ст. 20 ГС ГОСТ 8732-78 / ГОСТ 8731-74</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Труба 60х8, ст. 20 ГС ГОСТ 8732-78 / ГОСТ 8731-74</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>60×8</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>61.52</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0.06152</v>
-      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Труба 83×11, ст. 20 ГОСТ 8732-78 / 8731-74</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Труба 83х11, ст. 20 ГОСТ 8732-78 / 8731-74</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>83×11</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>117.13</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0.11713</v>
-      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0.79765</v>
+      <c r="F9" s="7" t="n">
+        <v>0.7976</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования (весь лот, метод сопоставимых рыночных цен, поштучная цена не раскрыта):</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>1838283.26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>2242705.58</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="140" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ЛОТ СМЕШАННЫЙ («Закупка металлопроката (4917)», АО «ЦКБ ТМ», запрос котировок среди СМП): «Форма 3. Спецификация согласно проекту договора» (Приложение № 2 к извещению 11-ЗК/ЮЧ) содержит 39 позиций металлопроката в кг — двутавр (1), круг (2), лист (20), пруток алюминиевый (1), труба (8), уголок (1), швеллер (4). Из них 7 позиций — КРУГЛЫЕ СТАЛЬНЫЕ трубы (ГОСТ 8732-78/8731-74, 8734-75/8733-74, 10704-91/10705-80), показаны выше, суммарно 0,79765 т. Одна позиция «Труба АМг6.М.КР 52×6 ГОСТ 18475-82» (14 кг) — не сталь, алюминиевый сплав, в spec не включена. Форма 3 — БЛАНК для участника (графы «Цена за единицу»/«Сумма» пустые в шаблоне), поштучных цен источник не даёт: НМЦК 2 242 705,58 ₽ определён методом сопоставимых рыночных цен на ВСЮ спецификацию (39 позиций металлопроката), а не на трубы отдельно — делить его пропорционально по позициям нельзя (правило 20). Прежний автопарсер принял категории ОКПД2 из «ИЗВЕЩЕНИЕ 11-ЗК_ЮЧ.docx» (информационная карта) за позиции спецификации и разделил НМЦК на 8 категорий равными долями по 280 338,12 ₽ — это артефакт, реальные позиции и массы взяты из «Форма 3» того же документа.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 7 из 40 позиций; остальное — не трубы (двутавр, круг, лист, пруток, труба, уголок, …), в таблицу не включено. ИТОГО — только трубная часть, «НМЦК из обоснования» — весь лот.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Источник: ИЗВЕЩЕНИЕ 11-ЗК_ЮЧ.docx (Приложение №2, Форма 3 — Спецификация согласно проекту договора)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Источник: ИЗВЕЩЕНИЕ 11-ЗК_ ЮЧ.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A14:B16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340996426/spec-340996426.xlsx
+++ b/vse-loti/340996426/spec-340996426.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -747,7 +750,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>НМЦК с НДС 22%:</t>
+          <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -761,18 +764,25 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; суммы источника указаны с НДС: "(Два миллиона двести сорок две тысячи семьсот пять) рублей 58 копеек, с учетом всех налогов, сборов и иных обязательных платежей." — ИЗВЕЩЕНИЕ 11-ЗК_ ЮЧ.docx. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Источник: ИЗВЕЩЕНИЕ 11-ЗК_ ЮЧ.docx</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="A15:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340996426/spec-340996426.xlsx
+++ b/vse-loti/340996426/spec-340996426.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -482,6 +482,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -517,17 +518,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -556,7 +562,7 @@
       <c r="F2" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -584,7 +590,7 @@
       <c r="F3" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -612,7 +618,7 @@
       <c r="F4" s="4" t="n">
         <v>0.252</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -640,7 +646,7 @@
       <c r="F5" s="4" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -668,7 +674,7 @@
       <c r="F6" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -696,7 +702,7 @@
       <c r="F7" s="4" t="n">
         <v>0.0615</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -724,65 +730,700 @@
       <c r="F8" s="4" t="n">
         <v>0.1171</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
+          <t>Прочие позиции лота (33) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Двутавр 45Б2, С345-12-св СТО АСЧМ 20-93 / ГОСТ 27772-2021</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>3648</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Круг 16, 15-ГС ГОСТ 2590-06 / 1050-88</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Круг 25, 45 ГОСТ 2590-06 / 1050-13</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Лист 0,5, К270В6-III-08пс-св ГОСТ 19904-90 / 16523-97</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Лист 1, К310В4-III-15пс-св ГОСТ 19904-74 / 16523-90</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Лист 10, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Лист 10, Ст3сп5-св ГОСТ 19903-74 / 14637-89</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Лист 12, 345-09Г2С-св-15 ГС ГОСТ 19903-74 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Лист 14х1500х2000, 345-09Г2С-св-15 ГС ГОСТ 19903-74 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Лист 14х1500х2000, Ст3сп5-св ГОСТ 19903-15 / 14637-89</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Лист 16х1500х6000, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>1137</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Лист 2, К310В4-III-15пс-св ГОСТ 19904-90 / 16523-97</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Лист 20х1500х6000, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Лист 24, Ст3сп5-св ГОСТ 19903-15 / 14637-89</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Лист 25, 295-09Г2С-св-12 ГС ГОСТ 19903-74 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Лист 3, К310В4-III-15пс-св ГОСТ 19903-15 / 16523-97</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Лист 30х1500х1500, 345-09Г2С-св-15 ГС ГОСТ 19903-74 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="3" t="n">
+        <v>537</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Лист 4х1500х3000, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Лист 4х1500х6000, Ст3сп2-св ГОСТ 19903-15 / 14637-89</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Лист 50х1500х1500, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Лист 6х1500х6000, 345-09Г2С-св-15 ГС ГОСТ 19903-74 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Лист 6х1500х6000, Ст3сп5-св ГОСТ 19903-15 / 14637-89</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Лист 8х1500х6000, 345-09Г2С-св-15 ГОСТ 19903-15 / 19281-89</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="3" t="n">
+        <v>576</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Лист А5Н-0,5х1000х2000 ГОСТ 21631-76</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Лист А5Н-1,5х1000х2000 ГОСТ 21631-76</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Лист ромб. 4х1500х3000 (1 шт.), 4х1500х6000 (1шт.) Ст3кп2 ГОСТ 8568-77</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>481</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Пруток АМг6М.КР.35ПхНД ГОСТ 21488-97</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="5" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Труба АМг6.М.КР 52х6 ГОСТ 18475-82</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Уголок 50х50х5, Ст3кп2-св ГОСТ 8509-93 / 535-05</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="5" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер 10У, 325-09Г2С-св-15 ГОСТ 8240-97 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер 12У, 325-09Г2С-св-15 ГОСТ 8240-97 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер 20У, 325-09Г2С-св-12 ГОСТ 8240-97 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="3" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер 27У, 325-09Г2С-св-15 ГОСТ 8240-97 / 19281-14</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО трубная часть</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n">
         <v>0.7976</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="H44" s="8" t="n">
         <v>1838283.26</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="J45" s="8" t="n">
         <v>2242705.58</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Трубная часть лота: 7 из 40 позиций; остальное — не трубы (двутавр, круг, лист, пруток, труба, уголок, …), в таблицу не включено. ИТОГО — только трубная часть, «НМЦК из обоснования» — весь лот.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 7 из 40 позиций; остальное — не трубы (двутавр, круг, лист, пруток, труба, уголок, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; суммы источника указаны с НДС: "(Два миллиона двести сорок две тысячи семьсот пять) рублей 58 копеек, с учетом всех налогов, сборов и иных обязательных платежей." — ИЗВЕЩЕНИЕ 11-ЗК_ ЮЧ.docx. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Источник: ИЗВЕЩЕНИЕ 11-ЗК_ ЮЧ.docx</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="50"/>
+    <row r="51"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:B17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A49:B51"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
